--- a/4p-index/STP_PNGIRSU-2018-2023_4P-Index.xlsx
+++ b/4p-index/STP_PNGIRSU-2018-2023_4P-Index.xlsx
@@ -588,65 +588,51 @@
           <t>Updates the 2011–2016 PAGIRSU following a national waste-characterisation and data-tracking exercise (waste composition found to be approx. 58% biodegradable organics, 18% fines/inerts and 13% recyclables — of which plastics and glass each account for approx. 5% of total waste by weight — per PNGIRSU 2018-2023 data cited in the secondary source). Shifts the national approach from a collection-only focus towards a circular-economy model for municipal solid waste, setting strategic options and an action plan for 2018–2023, including: targets to compost up to 60% of the country's organic waste and substantially increase recycling; the roll-out of eco-centres, waste-processing centrals ('Centrais de Processamento de Resíduos') and composting stations; and the start of selective collection of glass, cans, plastics and batteries. Plastics are explicitly and repeatedly named in the underlying PNGIRSU waste-composition data and in the selective-collection and processing-central initiatives it documents/plans.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Exact original wording not available from the primary plan document (not located online). As reported in the task brief for this exercise: 'setting targets to compost up to 60% of the country's organic waste and heavily increase recycling.' This paraphrase is corroborated in substance, but not in exact wording, by the secondary source, which documents composting stations and processing centrals for recyclables (including plastics) as concrete implementation vehicles for the plan's circular-economy strategic options.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>National sector plan/strategy ('Plano Nacional') for waste management, prepared with technical assistance (TESE, Associação para o Desenvolvimento, March 2018) for the Government of São Tomé and Príncipe / Ministério dos Recursos Naturais, Energia e Ambiente. It sets strategic options, an action plan, and quantifiable targets (e.g., the 60% organic-waste composting target reported in the task brief), but was not enacted as legislation by the National Assembly nor issued as an executive decree/regulation — scored as a strategy/plan incorporating quantifiable targets (0.5) rather than legislation (1) or a regulation (0.75).</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>waste management, municipalities, environment, agriculture, health, industry, construction</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K2" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="M2" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>No dedicated, ring-fenced PNGIRSU fund or budget line was identified in the material located for this exercise. The secondary source lists multiple external financiers and technical-assistance providers active in STP's waste-management sector during the PNGIRSU period, without confirming a single consolidated PNGIRSU budget: 'As entidades de maior destaque no financiamento e assistência técnica em gestão de resíduos em STP são: União Europeia, Instituto Camões, Fundo Português de Carbono, União das Cidades Capitais de Língua Portuguesa (UCCLA), Cooperação Portuguesa, AECID, Governo do Japão, Banco Africano de Desenvolvimento, USAID e AUSTRALIAID.' / 'The most prominent entities financing and providing technical assistance for waste management in STP are: the European Union, the Camões Institute, the Portuguese Carbon Fund, the Union of Capital Cities of Portuguese Language (UCCLA), Portuguese Cooperation, AECID, the Government of Japan, the African Development Bank, USAID and AusAID.' Specific initiatives it documents (e.g., the Lobata processing central under the EU/TESE-backed 'ValoRES' project) had identified funders, but a consolidated ring-fenced PNGIRSU implementation fund was not confirmed — coded as M = 0.5 (funding/funding sources mentioned, not shown to be ring-fenced) rather than M = 1.</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+      <c r="O2" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0.8</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -658,25 +644,19 @@
           <t>PNGIRSU 2018-2023 sets a strategic target to compost up to 60% of the country's organic waste (as reported in the task brief for this exercise; exact wording not verified against the primary text) and documents/plans a network of composting facilities as the implementation vehicle. Facilities corroborated in the secondary source (citing PNGIRSU 2018-2023 data) include: the 'Ecocentro de Caué' (established 2015; run by the 'Entidade de Resíduos de Interesse Comunitário de Caué' with 3 staff; sorts organics and some recyclables — cans, plastic and glass bottles — and produces approx. 14 t of compost/year); the 'Estação de Compostagem do Príncipe' (operating since 2016, run by the 'Cooperativa das Senhoras da Porto Real'; approx. 35 t of compost/year, sold at 5 STN/kg); and the organic-waste valorisation station at Correia, Água Grande (established 2013 under a UCCLA-funded project; pilot capacity of 600–1,000 t/year of mixed household bio-waste, urban green waste and other biodegradables; transferred from the Água Grande District Chamber to the Ministry of Agriculture and Rural Development from 2015).</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Authority: each facility has a named operating entity (a community-waste association in Caué, a women's cooperative in Príncipe, and — since 2015 — the Ministry of Agriculture and Rural Development in Água Grande) (+0.25). Monitoring: annual compost-output quantities are tracked and reported (approx. 14 t and 35 t/year respectively), evidencing some data-collection practice (+0.25). No enforcement mechanism is evidenced — these are voluntary/cooperative-run facilities, not backed by penalties for non-composting (0). Not unconditional: the Correia station is explicitly described as still in a 'fase piloto' / 'pilot phase', and the 60% target's achievement status could not be verified (0).</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="V2" s="2" t="n">
+        <v>0.65</v>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
@@ -705,65 +685,51 @@
           <t>Updates the 2011–2016 PAGIRSU following a national waste-characterisation and data-tracking exercise (waste composition found to be approx. 58% biodegradable organics, 18% fines/inerts and 13% recyclables — of which plastics and glass each account for approx. 5% of total waste by weight — per PNGIRSU 2018-2023 data cited in the secondary source). Shifts the national approach from a collection-only focus towards a circular-economy model for municipal solid waste, setting strategic options and an action plan for 2018–2023, including: targets to compost up to 60% of the country's organic waste and substantially increase recycling; the roll-out of eco-centres, waste-processing centrals ('Centrais de Processamento de Resíduos') and composting stations; and the start of selective collection of glass, cans, plastics and batteries. Plastics are explicitly and repeatedly named in the underlying PNGIRSU waste-composition data and in the selective-collection and processing-central initiatives it documents/plans.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Exact original wording not available from the primary plan document (not located online). As reported in the task brief for this exercise: 'setting targets to compost up to 60% of the country's organic waste and heavily increase recycling.' This paraphrase is corroborated in substance, but not in exact wording, by the secondary source, which documents composting stations and processing centrals for recyclables (including plastics) as concrete implementation vehicles for the plan's circular-economy strategic options.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>National sector plan/strategy ('Plano Nacional') for waste management, prepared with technical assistance (TESE, Associação para o Desenvolvimento, March 2018) for the Government of São Tomé and Príncipe / Ministério dos Recursos Naturais, Energia e Ambiente. It sets strategic options, an action plan, and quantifiable targets (e.g., the 60% organic-waste composting target reported in the task brief), but was not enacted as legislation by the National Assembly nor issued as an executive decree/regulation — scored as a strategy/plan incorporating quantifiable targets (0.5) rather than legislation (1) or a regulation (0.75).</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>waste management, municipalities, environment, agriculture, health, industry, construction</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K3" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="M3" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>No dedicated, ring-fenced PNGIRSU fund or budget line was identified in the material located for this exercise. The secondary source lists multiple external financiers and technical-assistance providers active in STP's waste-management sector during the PNGIRSU period, without confirming a single consolidated PNGIRSU budget: 'As entidades de maior destaque no financiamento e assistência técnica em gestão de resíduos em STP são: União Europeia, Instituto Camões, Fundo Português de Carbono, União das Cidades Capitais de Língua Portuguesa (UCCLA), Cooperação Portuguesa, AECID, Governo do Japão, Banco Africano de Desenvolvimento, USAID e AUSTRALIAID.' / 'The most prominent entities financing and providing technical assistance for waste management in STP are: the European Union, the Camões Institute, the Portuguese Carbon Fund, the Union of Capital Cities of Portuguese Language (UCCLA), Portuguese Cooperation, AECID, the Government of Japan, the African Development Bank, USAID and AusAID.' Specific initiatives it documents (e.g., the Lobata processing central under the EU/TESE-backed 'ValoRES' project) had identified funders, but a consolidated ring-fenced PNGIRSU implementation fund was not confirmed — coded as M = 0.5 (funding/funding sources mentioned, not shown to be ring-fenced) rather than M = 1.</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+      <c r="O3" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.8</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -775,25 +741,19 @@
           <t>Roll-out of community 'eco-centres' for sorting of organic and recyclable waste at the local level. Corroborated example (PNGIRSU 2018-2023 data, per the secondary source): the 'Ecocentro de Caué', established in 2015 and run by the 'Entidade de Resíduos de Interesse Comunitário de Caué' with 3 staff, which sorts organics (fruit peel and green waste) and 'alguns recicláveis (latas, plástico e garrafas de vidro)' / 'some recyclables (cans, plastic and glass bottles)'; the sorted recyclable material is baled and transported to the Central de Processamento de Resíduos (CPR, waste-processing central; see Row 3), while the organic fraction is composted under cover.</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Authority: the 'Entidade de Resíduos de Interesse Comunitário de Caué' is explicitly named as the operator (+0.25). Monitoring: material flows are tracked (baled recyclables sent to the CPR; compost output quantified) (+0.25). No enforcement mechanism evidenced (this is a voluntary community sorting facility, not a mandatory scheme) (0). Not unconditional: described as a single-district example with 3 staff, not confirmed as a nationwide network (0).</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="V3" s="2" t="n">
+        <v>0.65</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
@@ -822,65 +782,51 @@
           <t>Updates the 2011–2016 PAGIRSU following a national waste-characterisation and data-tracking exercise (waste composition found to be approx. 58% biodegradable organics, 18% fines/inerts and 13% recyclables — of which plastics and glass each account for approx. 5% of total waste by weight — per PNGIRSU 2018-2023 data cited in the secondary source). Shifts the national approach from a collection-only focus towards a circular-economy model for municipal solid waste, setting strategic options and an action plan for 2018–2023, including: targets to compost up to 60% of the country's organic waste and substantially increase recycling; the roll-out of eco-centres, waste-processing centrals ('Centrais de Processamento de Resíduos') and composting stations; and the start of selective collection of glass, cans, plastics and batteries. Plastics are explicitly and repeatedly named in the underlying PNGIRSU waste-composition data and in the selective-collection and processing-central initiatives it documents/plans.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Exact original wording not available from the primary plan document (not located online). As reported in the task brief for this exercise: 'setting targets to compost up to 60% of the country's organic waste and heavily increase recycling.' This paraphrase is corroborated in substance, but not in exact wording, by the secondary source, which documents composting stations and processing centrals for recyclables (including plastics) as concrete implementation vehicles for the plan's circular-economy strategic options.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>National sector plan/strategy ('Plano Nacional') for waste management, prepared with technical assistance (TESE, Associação para o Desenvolvimento, March 2018) for the Government of São Tomé and Príncipe / Ministério dos Recursos Naturais, Energia e Ambiente. It sets strategic options, an action plan, and quantifiable targets (e.g., the 60% organic-waste composting target reported in the task brief), but was not enacted as legislation by the National Assembly nor issued as an executive decree/regulation — scored as a strategy/plan incorporating quantifiable targets (0.5) rather than legislation (1) or a regulation (0.75).</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>waste management, municipalities, environment, agriculture, health, industry, construction</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K4" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="M4" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>No dedicated, ring-fenced PNGIRSU fund or budget line was identified in the material located for this exercise. The secondary source lists multiple external financiers and technical-assistance providers active in STP's waste-management sector during the PNGIRSU period, without confirming a single consolidated PNGIRSU budget: 'As entidades de maior destaque no financiamento e assistência técnica em gestão de resíduos em STP são: União Europeia, Instituto Camões, Fundo Português de Carbono, União das Cidades Capitais de Língua Portuguesa (UCCLA), Cooperação Portuguesa, AECID, Governo do Japão, Banco Africano de Desenvolvimento, USAID e AUSTRALIAID.' / 'The most prominent entities financing and providing technical assistance for waste management in STP are: the European Union, the Camões Institute, the Portuguese Carbon Fund, the Union of Capital Cities of Portuguese Language (UCCLA), Portuguese Cooperation, AECID, the Government of Japan, the African Development Bank, USAID and AusAID.' Specific initiatives it documents (e.g., the Lobata processing central under the EU/TESE-backed 'ValoRES' project) had identified funders, but a consolidated ring-fenced PNGIRSU implementation fund was not confirmed — coded as M = 0.5 (funding/funding sources mentioned, not shown to be ring-fenced) rather than M = 1.</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+      <c r="O4" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0.8</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
@@ -892,25 +838,19 @@
           <t>Roll-out of 'Centrais de Processamento de Resíduos' (CPR, waste-processing centrals) that receive sorted recyclables and transform them into inputs for civil construction. Corroborated example (PNGIRSU 2018-2023 data, per the secondary source): the CPR in Lobata (Ferreira Governo), inaugurated in 2016 under the EU/TESE-backed 'ValoRES' ('Valorizando Resíduos Criamos Emprego' / 'Valuing Waste, We Create Jobs') project, which receives waste from the Caué, Lembá and Água Grande districts — '47 toneladas [de vidro] e 5 toneladas de embalagens de plásticos e latas' / '47 tonnes [of glass] and 5 tonnes of plastic packaging and cans' — and processes it into different granulometries for use in civil construction in São Tomé and Príncipe.</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Authority: the CPR is operated under the ValoRES project (TESE, with EU funding) (+0.25). Monitoring: annual input tonnages by material stream are tracked and reported (47 t glass, 5 t plastic packaging/cans) (+0.25). No enforcement mechanism evidenced (0). Not unconditional: a footnote in the secondary source notes that, at the time of reporting, collected cans, plastics and battery/accumulator waste were 'acondicionados e aguardam encaminhamento para destino final através da exportação' / 'packaged and awaiting onward routing to final destination via export' — i.e., not all material streams had a confirmed local processing/end-market route (0).</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="V4" s="2" t="n">
+        <v>0.65</v>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
@@ -939,65 +879,51 @@
           <t>Updates the 2011–2016 PAGIRSU following a national waste-characterisation and data-tracking exercise (waste composition found to be approx. 58% biodegradable organics, 18% fines/inerts and 13% recyclables — of which plastics and glass each account for approx. 5% of total waste by weight — per PNGIRSU 2018-2023 data cited in the secondary source). Shifts the national approach from a collection-only focus towards a circular-economy model for municipal solid waste, setting strategic options and an action plan for 2018–2023, including: targets to compost up to 60% of the country's organic waste and substantially increase recycling; the roll-out of eco-centres, waste-processing centrals ('Centrais de Processamento de Resíduos') and composting stations; and the start of selective collection of glass, cans, plastics and batteries. Plastics are explicitly and repeatedly named in the underlying PNGIRSU waste-composition data and in the selective-collection and processing-central initiatives it documents/plans.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Exact original wording not available from the primary plan document (not located online). As reported in the task brief for this exercise: 'setting targets to compost up to 60% of the country's organic waste and heavily increase recycling.' This paraphrase is corroborated in substance, but not in exact wording, by the secondary source, which documents composting stations and processing centrals for recyclables (including plastics) as concrete implementation vehicles for the plan's circular-economy strategic options.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>National sector plan/strategy ('Plano Nacional') for waste management, prepared with technical assistance (TESE, Associação para o Desenvolvimento, March 2018) for the Government of São Tomé and Príncipe / Ministério dos Recursos Naturais, Energia e Ambiente. It sets strategic options, an action plan, and quantifiable targets (e.g., the 60% organic-waste composting target reported in the task brief), but was not enacted as legislation by the National Assembly nor issued as an executive decree/regulation — scored as a strategy/plan incorporating quantifiable targets (0.5) rather than legislation (1) or a regulation (0.75).</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>waste management, municipalities, environment, agriculture, health, industry, construction</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K5" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="M5" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>No dedicated, ring-fenced PNGIRSU fund or budget line was identified in the material located for this exercise. The secondary source lists multiple external financiers and technical-assistance providers active in STP's waste-management sector during the PNGIRSU period, without confirming a single consolidated PNGIRSU budget: 'As entidades de maior destaque no financiamento e assistência técnica em gestão de resíduos em STP são: União Europeia, Instituto Camões, Fundo Português de Carbono, União das Cidades Capitais de Língua Portuguesa (UCCLA), Cooperação Portuguesa, AECID, Governo do Japão, Banco Africano de Desenvolvimento, USAID e AUSTRALIAID.' / 'The most prominent entities financing and providing technical assistance for waste management in STP are: the European Union, the Camões Institute, the Portuguese Carbon Fund, the Union of Capital Cities of Portuguese Language (UCCLA), Portuguese Cooperation, AECID, the Government of Japan, the African Development Bank, USAID and AusAID.' Specific initiatives it documents (e.g., the Lobata processing central under the EU/TESE-backed 'ValoRES' project) had identified funders, but a consolidated ring-fenced PNGIRSU implementation fund was not confirmed — coded as M = 0.5 (funding/funding sources mentioned, not shown to be ring-fenced) rather than M = 1.</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+      <c r="O5" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0.8</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
@@ -1009,25 +935,19 @@
           <t>Start of selective (source-separated) collection of glass, cans, plastics and batteries, as reported in the task brief for this exercise, feeding into the eco-centres and waste-processing centrals described in Rows 2–3. The underlying PNGIRSU 2018-2023 waste-composition survey explicitly tracks 'Plásticos de todos os tipos' (Plastics of all types) as approx. 5% of total waste by weight nationally, alongside glass (approx. 5%) and paper/cardboard, as part of a combined 13% recyclables fraction (per the secondary source's summary of PNGIRSU data).</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="S5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
           <t>Authority: District Chambers ('Câmaras Distritais') are the general collection-implementation body under the pre-existing legal framework (Decreto n.º 36/1999, Art. 13) referenced throughout the plan's institutional context (+0.25). No enforcement mechanism is evidenced for participation in selective collection (0). No dedicated monitoring mechanism for selective-collection coverage/rates specifically was identified in the located material, beyond the general waste-composition survey (0). Not unconditional: described as the 'start of' selective collection, implying partial/emerging rather than universal coverage (0).</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0.525</t>
-        </is>
+      <c r="V5" s="2" t="n">
+        <v>0.525</v>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
@@ -1056,65 +976,51 @@
           <t>Updates the 2011–2016 PAGIRSU following a national waste-characterisation and data-tracking exercise (waste composition found to be approx. 58% biodegradable organics, 18% fines/inerts and 13% recyclables — of which plastics and glass each account for approx. 5% of total waste by weight — per PNGIRSU 2018-2023 data cited in the secondary source). Shifts the national approach from a collection-only focus towards a circular-economy model for municipal solid waste, setting strategic options and an action plan for 2018–2023, including: targets to compost up to 60% of the country's organic waste and substantially increase recycling; the roll-out of eco-centres, waste-processing centrals ('Centrais de Processamento de Resíduos') and composting stations; and the start of selective collection of glass, cans, plastics and batteries. Plastics are explicitly and repeatedly named in the underlying PNGIRSU waste-composition data and in the selective-collection and processing-central initiatives it documents/plans.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Exact original wording not available from the primary plan document (not located online). As reported in the task brief for this exercise: 'setting targets to compost up to 60% of the country's organic waste and heavily increase recycling.' This paraphrase is corroborated in substance, but not in exact wording, by the secondary source, which documents composting stations and processing centrals for recyclables (including plastics) as concrete implementation vehicles for the plan's circular-economy strategic options.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>National sector plan/strategy ('Plano Nacional') for waste management, prepared with technical assistance (TESE, Associação para o Desenvolvimento, March 2018) for the Government of São Tomé and Príncipe / Ministério dos Recursos Naturais, Energia e Ambiente. It sets strategic options, an action plan, and quantifiable targets (e.g., the 60% organic-waste composting target reported in the task brief), but was not enacted as legislation by the National Assembly nor issued as an executive decree/regulation — scored as a strategy/plan incorporating quantifiable targets (0.5) rather than legislation (1) or a regulation (0.75).</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>waste management, municipalities, environment, agriculture, health, industry, construction</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K6" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="M6" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>No dedicated, ring-fenced PNGIRSU fund or budget line was identified in the material located for this exercise. The secondary source lists multiple external financiers and technical-assistance providers active in STP's waste-management sector during the PNGIRSU period, without confirming a single consolidated PNGIRSU budget: 'As entidades de maior destaque no financiamento e assistência técnica em gestão de resíduos em STP são: União Europeia, Instituto Camões, Fundo Português de Carbono, União das Cidades Capitais de Língua Portuguesa (UCCLA), Cooperação Portuguesa, AECID, Governo do Japão, Banco Africano de Desenvolvimento, USAID e AUSTRALIAID.' / 'The most prominent entities financing and providing technical assistance for waste management in STP are: the European Union, the Camões Institute, the Portuguese Carbon Fund, the Union of Capital Cities of Portuguese Language (UCCLA), Portuguese Cooperation, AECID, the Government of Japan, the African Development Bank, USAID and AusAID.' Specific initiatives it documents (e.g., the Lobata processing central under the EU/TESE-backed 'ValoRES' project) had identified funders, but a consolidated ring-fenced PNGIRSU implementation fund was not confirmed — coded as M = 0.5 (funding/funding sources mentioned, not shown to be ring-fenced) rather than M = 1.</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O6" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
@@ -1126,25 +1032,19 @@
           <t>The plan operates within, and reinforces, the multi-level institutional framework for waste management in STP: national policy-setting and coordination sits with the Ministry responsible for the environment (currently the Ministério das Obras Públicas, Infraestruturas, Recursos Naturais e Ambiente, MIRN) and, within it, the Direção Geral do Ambiente (DGA, solid/gaseous waste) and Direcção-Geral dos Recursos Naturais e Energia (DGRNE, liquid waste/effluents); implementation of collection, transport and disposal sits with the decentralised District Chambers ('Câmaras Distritais'), consistent with Decreto n.º 36/1999. Other line ministries (agriculture, health, education, tourism, industry, commerce) hold sector-specific waste responsibilities.</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>Authority: MIRN/DGA/DGRNE at national level and District Chambers at sub-national level are explicitly named, with defined role divisions (+0.25). Monitoring: DGA is described as coordinating national environmental data/reporting, including the waste-characterisation exercise underlying this plan (+0.25, see also Row 7). No enforcement mechanism specific to this institutional-coordination role is evidenced within the located material (0). Not unconditional: the secondary source explicitly notes that district Waste Management Plans remain unapproved and that 'as capacidades de colocar em prática os vários dispositivos... são deveras fracas' / 'the capacities to implement the various instruments... are indeed weak' (0).</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="V6" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
@@ -1173,65 +1073,51 @@
           <t>Updates the 2011–2016 PAGIRSU following a national waste-characterisation and data-tracking exercise (waste composition found to be approx. 58% biodegradable organics, 18% fines/inerts and 13% recyclables — of which plastics and glass each account for approx. 5% of total waste by weight — per PNGIRSU 2018-2023 data cited in the secondary source). Shifts the national approach from a collection-only focus towards a circular-economy model for municipal solid waste, setting strategic options and an action plan for 2018–2023, including: targets to compost up to 60% of the country's organic waste and substantially increase recycling; the roll-out of eco-centres, waste-processing centrals ('Centrais de Processamento de Resíduos') and composting stations; and the start of selective collection of glass, cans, plastics and batteries. Plastics are explicitly and repeatedly named in the underlying PNGIRSU waste-composition data and in the selective-collection and processing-central initiatives it documents/plans.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Exact original wording not available from the primary plan document (not located online). As reported in the task brief for this exercise: 'setting targets to compost up to 60% of the country's organic waste and heavily increase recycling.' This paraphrase is corroborated in substance, but not in exact wording, by the secondary source, which documents composting stations and processing centrals for recyclables (including plastics) as concrete implementation vehicles for the plan's circular-economy strategic options.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>National sector plan/strategy ('Plano Nacional') for waste management, prepared with technical assistance (TESE, Associação para o Desenvolvimento, March 2018) for the Government of São Tomé and Príncipe / Ministério dos Recursos Naturais, Energia e Ambiente. It sets strategic options, an action plan, and quantifiable targets (e.g., the 60% organic-waste composting target reported in the task brief), but was not enacted as legislation by the National Assembly nor issued as an executive decree/regulation — scored as a strategy/plan incorporating quantifiable targets (0.5) rather than legislation (1) or a regulation (0.75).</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>waste management, municipalities, environment, agriculture, health, industry, construction</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K7" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="M7" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>No dedicated, ring-fenced PNGIRSU fund or budget line was identified in the material located for this exercise. The secondary source lists multiple external financiers and technical-assistance providers active in STP's waste-management sector during the PNGIRSU period, without confirming a single consolidated PNGIRSU budget: 'As entidades de maior destaque no financiamento e assistência técnica em gestão de resíduos em STP são: União Europeia, Instituto Camões, Fundo Português de Carbono, União das Cidades Capitais de Língua Portuguesa (UCCLA), Cooperação Portuguesa, AECID, Governo do Japão, Banco Africano de Desenvolvimento, USAID e AUSTRALIAID.' / 'The most prominent entities financing and providing technical assistance for waste management in STP are: the European Union, the Camões Institute, the Portuguese Carbon Fund, the Union of Capital Cities of Portuguese Language (UCCLA), Portuguese Cooperation, AECID, the Government of Japan, the African Development Bank, USAID and AusAID.' Specific initiatives it documents (e.g., the Lobata processing central under the EU/TESE-backed 'ValoRES' project) had identified funders, but a consolidated ring-fenced PNGIRSU implementation fund was not confirmed — coded as M = 0.5 (funding/funding sources mentioned, not shown to be ring-fenced) rather than M = 1.</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O7" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
@@ -1243,25 +1129,19 @@
           <t>PNGIRSU 2018-2023 documents and projects generation of special waste streams that may be hazardous — '(i) Solventes e tintas; (ii) Pneus; (iii) Óleos usados (motores, máquinas); (iv) Resíduos de Equipamentos Elétricos e Eletrónicos; e (v) Veículos em Fim de Vida' / '(i) solvents and paints; (ii) tyres; (iii) used oils (engines, machinery); (iv) waste electrical and electronic equipment (WEEE); and (v) end-of-life vehicles' — projecting this waste class to reach 742 and 758 tonnes/year in 2022 and 2023 respectively, as a planning basis for future dedicated management measures.</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="S7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>Authority: implicitly the same MIRN/DGA institutional structure as Row 5, though no dedicated authority specifically for this waste class is named in the located material (0). Monitoring: the plan itself contains a quantified generation projection for this waste class by year, evidencing a monitoring/forecasting exercise (+0.25). No enforcement mechanism evidenced (0). Not unconditional: presented as a projection/planning input rather than a binding management requirement (0).</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0.225</t>
-        </is>
+      <c r="V7" s="2" t="n">
+        <v>0.225</v>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
@@ -1290,65 +1170,51 @@
           <t>Updates the 2011–2016 PAGIRSU following a national waste-characterisation and data-tracking exercise (waste composition found to be approx. 58% biodegradable organics, 18% fines/inerts and 13% recyclables — of which plastics and glass each account for approx. 5% of total waste by weight — per PNGIRSU 2018-2023 data cited in the secondary source). Shifts the national approach from a collection-only focus towards a circular-economy model for municipal solid waste, setting strategic options and an action plan for 2018–2023, including: targets to compost up to 60% of the country's organic waste and substantially increase recycling; the roll-out of eco-centres, waste-processing centrals ('Centrais de Processamento de Resíduos') and composting stations; and the start of selective collection of glass, cans, plastics and batteries. Plastics are explicitly and repeatedly named in the underlying PNGIRSU waste-composition data and in the selective-collection and processing-central initiatives it documents/plans.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Exact original wording not available from the primary plan document (not located online). As reported in the task brief for this exercise: 'setting targets to compost up to 60% of the country's organic waste and heavily increase recycling.' This paraphrase is corroborated in substance, but not in exact wording, by the secondary source, which documents composting stations and processing centrals for recyclables (including plastics) as concrete implementation vehicles for the plan's circular-economy strategic options.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G8" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>National sector plan/strategy ('Plano Nacional') for waste management, prepared with technical assistance (TESE, Associação para o Desenvolvimento, March 2018) for the Government of São Tomé and Príncipe / Ministério dos Recursos Naturais, Energia e Ambiente. It sets strategic options, an action plan, and quantifiable targets (e.g., the 60% organic-waste composting target reported in the task brief), but was not enacted as legislation by the National Assembly nor issued as an executive decree/regulation — scored as a strategy/plan incorporating quantifiable targets (0.5) rather than legislation (1) or a regulation (0.75).</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>waste management, municipalities, environment, agriculture, health, industry, construction</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K8" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="M8" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>No dedicated, ring-fenced PNGIRSU fund or budget line was identified in the material located for this exercise. The secondary source lists multiple external financiers and technical-assistance providers active in STP's waste-management sector during the PNGIRSU period, without confirming a single consolidated PNGIRSU budget: 'As entidades de maior destaque no financiamento e assistência técnica em gestão de resíduos em STP são: União Europeia, Instituto Camões, Fundo Português de Carbono, União das Cidades Capitais de Língua Portuguesa (UCCLA), Cooperação Portuguesa, AECID, Governo do Japão, Banco Africano de Desenvolvimento, USAID e AUSTRALIAID.' / 'The most prominent entities financing and providing technical assistance for waste management in STP are: the European Union, the Camões Institute, the Portuguese Carbon Fund, the Union of Capital Cities of Portuguese Language (UCCLA), Portuguese Cooperation, AECID, the Government of Japan, the African Development Bank, USAID and AusAID.' Specific initiatives it documents (e.g., the Lobata processing central under the EU/TESE-backed 'ValoRES' project) had identified funders, but a consolidated ring-fenced PNGIRSU implementation fund was not confirmed — coded as M = 0.5 (funding/funding sources mentioned, not shown to be ring-fenced) rather than M = 1.</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O8" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
@@ -1360,25 +1226,19 @@
           <t>PNGIRSU 2018-2023 is founded on a national waste-characterisation and data-tracking exercise (per the task brief, approx. one year of national waste data tracking preceded the plan), producing district-level data on waste generation (national average 0.39 kg/capita/day; total 197,700 t/year as of 2018), collection coverage (national average 38%, ranging from 25% in the Autonomous Region of Príncipe to 81% in Caué), and a national waste-composition breakdown that explicitly tracks 'Plásticos de todos os tipos' (Plastics of all types) as a distinct category (approx. 5% of total waste by weight), alongside biodegradables (approx. 58%), fines/inerts (approx. 18%), paper/cardboard, glass (approx. 5%), textiles, metals, complex materials and hazardous/hospital waste/batteries.</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
           <t>Authority: the data collection and characterisation exercise was carried out for the Government of STP under PNGIRSU with technical assistance (TESE, 2018) (+0.25). Monitoring: this instrument is itself the plan's core data/monitoring mechanism — district-level generation, collection-coverage and composition data are compiled and reported (+0.25). No enforcement mechanism applicable to a data-collection exercise (0). Not unconditional: the secondary source notes gaps and likely need for correction in some of the derived per-capita figures when extrapolated to later years (0).</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="V8" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
